--- a/duoki_editor/resources/data/blank/服装店-一般疑问句_肯定答句跟读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/服装店-一般疑问句_肯定答句跟读-1-blank.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
   <si>
     <t>stage_id</t>
   </si>
@@ -52,7 +52,7 @@
     <t>一般疑问句_示范_2_问</t>
   </si>
   <si>
-    <t>(一般疑问句_示范_1_答)</t>
+    <t>一般疑问句_示范_1_答</t>
   </si>
   <si>
     <t>一般疑问句_示范_2_答</t>
@@ -91,6 +91,9 @@
     <t>一般疑问句_跟读_3_答</t>
   </si>
   <si>
+    <t>一般疑问句_跟读_帮助</t>
+  </si>
+  <si>
     <t>结束语_1</t>
   </si>
   <si>
@@ -106,7 +109,7 @@
     <t>{npc2_name}，明天我们就要去旅行了，我们来检查一下行李吧！{sentence_question_cn}？{sentence_question_en}?</t>
   </si>
   <si>
-    <t>哦，目的地天气变化很快哦！也许我们可以去游泳！你有泳衣吗？Have you got swimsuit？</t>
+    <t>哦，目的地天气变化很快哦！也许我们可以去游泳！你有泳衣吗？Have you got a swimsuit？</t>
   </si>
   <si>
     <t>{sentence_answer_en_1}。 {sentence_answer_cn_1} 。</t>
@@ -115,13 +118,13 @@
     <t>{sentence_answer_en_2}。 {sentence_answer_cn_2}。{user_name}，如果你也去旅行，你会带哪些衣物呢？赶紧准备起来吧！</t>
   </si>
   <si>
-    <t>我很喜欢旅行，让我们先把要带上的衣物找出来吧！第一件衣物是{word_cn}吧！"[{word_en}]"</t>
+    <t>我很喜欢旅行，让我们先把要带上的衣物找出来吧！第一件衣物是{word_cn}！"[{word_en}]"</t>
   </si>
   <si>
     <t>第二件衣物是，{word_cn}！"[{word_en}]"</t>
   </si>
   <si>
-    <t>这是最后这件衣物是，{word_cn}吧！"[{word_en}]"</t>
+    <t>最后这件衣物是，{word_cn}！"[{word_en}]"</t>
   </si>
   <si>
     <t>我来帮你吧！"[{word_en}]"</t>
@@ -540,10 +543,10 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -557,10 +560,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -574,10 +577,10 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -591,10 +594,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -608,10 +611,10 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -625,10 +628,10 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -642,10 +645,10 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -659,10 +662,10 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -676,10 +679,10 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -693,10 +696,10 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -710,10 +713,10 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -727,10 +730,10 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -744,10 +747,10 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -761,10 +764,10 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -778,10 +781,10 @@
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -792,13 +795,13 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -809,13 +812,13 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
